--- a/Entregables/Cronograma-26-08.xlsx
+++ b/Entregables/Cronograma-26-08.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frbautneduar-my.sharepoint.com/personal/jomansilla_frba_utn_edu_ar/Documents/04-Cuarto-Año-2026/Administracion-De-Sistemas-De-Información/TPA/Entregables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="11_F25DC773A252ABDACC1048BDA95E51B25BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7982797-8018-4F3F-8A3D-1D7E81A02D03}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="11_F25DC773A252ABDACC1048BDA95E51B25BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74C9846C-7504-4038-9A04-91498943DE97}"/>
   <bookViews>
-    <workbookView xWindow="8100" yWindow="3360" windowWidth="26085" windowHeight="17235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="165">
   <si>
     <t>Name</t>
   </si>
@@ -528,13 +528,38 @@
   </si>
   <si>
     <t>DevOps, Soporte, Arq de Software, Backend, Frontend</t>
+  </si>
+  <si>
+    <r>
+      <t>“Desarrollo e implementación de la p</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>lataforma Integral para la Gestión y Administración de Becas Académicas (Beca360)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>”</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,6 +583,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -579,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -610,6 +649,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,13 +735,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4554F5A-E637-4EFB-A1FD-A4A733E8795F}" name="Table1" displayName="Table1" ref="B2:H63" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="B2:H63" xr:uid="{C4554F5A-E637-4EFB-A1FD-A4A733E8795F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4554F5A-E637-4EFB-A1FD-A4A733E8795F}" name="Table1" displayName="Table1" ref="B3:H64" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="B3:H64" xr:uid="{C4554F5A-E637-4EFB-A1FD-A4A733E8795F}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{34F31C3C-8A04-493B-B2BC-E380E6F2C306}" name="Name" totalsRowLabel="Total" dataDxfId="13" totalsRowDxfId="12"/>
     <tableColumn id="8" xr3:uid="{BC2A692D-7633-4C99-BC67-0BB5986E0EE8}" name="Duration" dataDxfId="11" totalsRowDxfId="10"/>
@@ -976,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H63"/>
+  <dimension ref="A2:H64"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -990,112 +1028,97 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1">
-        <v>2</v>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -1104,13 +1127,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>19</v>
@@ -1118,22 +1141,22 @@
     </row>
     <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>19</v>
@@ -1144,48 +1167,48 @@
     </row>
     <row r="8" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="1">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>11</v>
@@ -1196,103 +1219,103 @@
     </row>
     <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1">
         <v>6</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1">
         <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>42</v>
@@ -1300,10 +1323,10 @@
     </row>
     <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
@@ -1315,7 +1338,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>42</v>
@@ -1326,10 +1349,10 @@
     </row>
     <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
@@ -1352,10 +1375,10 @@
     </row>
     <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
@@ -1378,10 +1401,10 @@
     </row>
     <row r="17" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>14</v>
@@ -1393,36 +1416,36 @@
         <v>13</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>144</v>
+      <c r="D18" s="1">
+        <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>49</v>
@@ -1430,48 +1453,48 @@
     </row>
     <row r="19" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="1">
-        <v>16</v>
+      <c r="D19" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>34</v>
@@ -1482,22 +1505,22 @@
     </row>
     <row r="21" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>34</v>
@@ -1508,88 +1531,88 @@
     </row>
     <row r="22" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>58</v>
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D24" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>14</v>
@@ -1601,7 +1624,7 @@
         <v>17</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>62</v>
@@ -1612,10 +1635,10 @@
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>14</v>
@@ -1627,33 +1650,33 @@
         <v>17</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D27" s="1">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>62</v>
@@ -1664,74 +1687,74 @@
     </row>
     <row r="28" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D28" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>75</v>
+      <c r="D30" s="1">
+        <v>26</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>57</v>
@@ -1742,22 +1765,22 @@
     </row>
     <row r="31" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="1">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>57</v>
@@ -1768,334 +1791,334 @@
     </row>
     <row r="32" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D32" s="1">
         <v>28</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>82</v>
+        <v>30</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="D33" s="1">
         <v>28</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>149</v>
+        <v>8</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>67</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="1">
+        <v>28</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>32</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35" s="1">
         <v>30</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35">
+    <row r="36" spans="1:8" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>33</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="1">
+      <c r="C36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="1">
         <v>31</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F36" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D36" s="1">
-        <v>32</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>89</v>
       </c>
       <c r="H36" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="1">
+        <v>32</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37">
+    <row r="38" spans="1:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>35</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="1">
+      <c r="C38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="1">
         <v>33</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F38" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="1">
-        <v>34</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>93</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D39" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D40" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D41" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>102</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D43" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>107</v>
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>44</v>
+        <v>152</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>81</v>
@@ -2106,114 +2129,114 @@
     </row>
     <row r="45" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="D45" s="1">
         <v>40</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>112</v>
+        <v>43</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="D46" s="1">
         <v>40</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>110</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D47" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>153</v>
+        <v>13</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D48" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>14</v>
@@ -2225,21 +2248,21 @@
         <v>17</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>14</v>
@@ -2251,7 +2274,7 @@
         <v>17</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>118</v>
@@ -2262,100 +2285,100 @@
     </row>
     <row r="51" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D51" s="1">
-        <v>45.46</v>
+        <v>44</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D52" s="1">
-        <v>47</v>
+        <v>45.46</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>127</v>
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D54" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>111</v>
@@ -2366,88 +2389,88 @@
     </row>
     <row r="55" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>32</v>
+        <v>127</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D55" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>14</v>
+        <v>53</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="D56" s="1">
         <v>49</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>125</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D57" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>14</v>
@@ -2459,47 +2482,47 @@
         <v>17</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D59" s="1">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>14</v>
@@ -2508,10 +2531,10 @@
         <v>54</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>139</v>
@@ -2522,48 +2545,48 @@
     </row>
     <row r="61" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D61" s="1">
-        <v>54.55</v>
+        <v>54</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D62" s="1">
-        <v>56</v>
+        <v>54.55</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>130</v>
@@ -2574,22 +2597,22 @@
     </row>
     <row r="63" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>143</v>
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D63" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>130</v>
@@ -2598,7 +2621,36 @@
         <v>130</v>
       </c>
     </row>
+    <row r="64" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="1">
+        <v>57</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
